--- a/files/港岛-半山区西部-21 Borrett Road 第1期.xlsx
+++ b/files/港岛-半山区西部-21 Borrett Road 第1期.xlsx
@@ -8,9 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1号及2号 销控表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3号及5号 销控表" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6号及7号 销控表" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -113,42 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -178,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -194,45 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -704,7 +569,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-03-02</t>
         </is>
       </c>
       <c r="H3" s="5" t="n">
@@ -996,7 +861,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-06-22</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1042,7 +907,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-15</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1088,7 +953,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-27</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1134,7 +999,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-27</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1230,7 +1095,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-29</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1276,7 +1141,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-01</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1322,7 +1187,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-05</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1368,7 +1233,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1414,7 +1279,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-04-14</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1460,7 +1325,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-24</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1506,7 +1371,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-03-23</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -1552,7 +1417,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-05</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -1690,7 +1555,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-11-15</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -2532,7 +2397,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-10</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -2578,7 +2443,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-11-23</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -2624,7 +2489,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-11-23</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -2920,7 +2785,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-06</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -3016,7 +2881,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-29</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -3112,7 +2977,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-28</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -3400,7 +3265,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-04</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -4434,7 +4299,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-04-15</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -4480,7 +4345,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-08-02</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -4526,7 +4391,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-08-02</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -4572,7 +4437,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-06-01</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -4618,7 +4483,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-06-01</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -4764,7 +4629,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-08-15</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -4810,7 +4675,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-11-15</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
@@ -4856,7 +4721,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-10-20</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
@@ -4902,7 +4767,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-30</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
@@ -4948,7 +4813,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-10-18</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
@@ -5044,7 +4909,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-10-18</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -5090,7 +4955,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-10-11</t>
         </is>
       </c>
       <c r="H94" s="5" t="n">
@@ -5136,7 +5001,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-04-26</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -5182,7 +5047,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-09</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
@@ -5324,7 +5189,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-02</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
@@ -5420,7 +5285,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-03-20</t>
         </is>
       </c>
       <c r="H101" s="5" t="n">
@@ -6188,7 +6053,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-10-21</t>
         </is>
       </c>
       <c r="H117" s="5" t="n">
@@ -6256,1673 +6121,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F24"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>21 Borrett Road 第1期 - 1号及2号 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>38 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>18 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>20 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>1 | 3309呎 (4+房)
-$45,941万
-$138,836/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B7" s="18" t="inlineStr">
-        <is>
-          <t>1 | 2945呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="18" t="inlineStr">
-        <is>
-          <t>2 | 2154呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>1 | 2945呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>2 | 2154呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>1 | 2886呎 (4+房)
-$27,063万
-$93,775/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>2 | 2096呎 (4+房)
-$18,080万
-$86,260/呎
-(23年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>1 | 2886呎 (4+房)
-$25,000万
-$86,625/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>2 | 2096呎 (4+房)
-$16,952万
-$80,878/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B11" s="18" t="inlineStr">
-        <is>
-          <t>1 | 2945呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>2 | 2096呎 (4+房)
-$17,000万
-$81,107/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>1 | 2945呎 (4+房)
-$23,854万
-$81,000/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>2 | 2096呎 (4+房)
-$16,000万
-$76,336/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>1 | 2886呎 (4+房)
-$23,280万
-$80,665/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>2 | 2096呎 (4+房)
-$15,500万
-$73,950/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>1 | 2886呎 (4+房)
-$23,146万
-$80,201/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>2 | 2154呎 (4+房)
-$15,078万
-$70,000/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>1 | 2886呎 (4+房)
-$22,971万
-$79,595/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>2 | 2096呎 (4+房)
-$14,550万
-$69,418/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>1 | 2886呎 (4+房)
-$21,035万
-$72,885/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>2 | 2096呎 (4+房)
-$13,600万
-$64,885/呎
-(24年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>1 | 2886呎 (4+房)
-$21,800万
-$75,537/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>2 | 2154呎 (4+房)
-$13,300万
-$61,746/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t>1 | 2945呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C18" s="18" t="inlineStr">
-        <is>
-          <t>2 | 2154呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>1 | 2945呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C19" s="18" t="inlineStr">
-        <is>
-          <t>2 | 2154呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>1 | 2945呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="inlineStr">
-        <is>
-          <t>2 | 2154呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B21" s="18" t="inlineStr">
-        <is>
-          <t>1 | 2945呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C21" s="18" t="inlineStr">
-        <is>
-          <t>2 | 2154呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B22" s="18" t="inlineStr">
-        <is>
-          <t>1 | 2945呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C22" s="18" t="inlineStr">
-        <is>
-          <t>2 | 2154呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B23" s="18" t="inlineStr">
-        <is>
-          <t>1 | 2945呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C23" s="18" t="inlineStr">
-        <is>
-          <t>2 | 2154呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B24" s="18" t="inlineStr">
-        <is>
-          <t>1 | 2876呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C24" s="18" t="inlineStr">
-        <is>
-          <t>2 | 2075呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>21 Borrett Road 第1期 - 3号及5号 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>39 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>12 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>27 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>3 | 2664呎 (4+房)
-$34,411万
-$129,169/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>3 | 2133呎 (4+房)
-$20,000万
-$93,765/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>5 | 2109呎 (4+房)
-$18,600万
-$88,193/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>3 | 2193呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>5 | 2166呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B9" s="18" t="inlineStr">
-        <is>
-          <t>3 | 2193呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="18" t="inlineStr">
-        <is>
-          <t>5 | 2166呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>3 | 2133呎 (4+房)
-$17,680万
-$82,888/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="inlineStr">
-        <is>
-          <t>5 | 2166呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>3 | 2133呎 (4+房)
-$17,200万
-$80,638/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C11" s="18" t="inlineStr">
-        <is>
-          <t>5 | 2166呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>3 | 2133呎 (4+房)
-$16,780万
-$78,669/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C12" s="18" t="inlineStr">
-        <is>
-          <t>5 | 2166呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>3 | 2133呎 (4+房)
-$16,200万
-$75,949/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="inlineStr">
-        <is>
-          <t>5 | 2166呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>3 | 2133呎 (4+房)
-$15,600万
-$73,136/呎
-(24年-12月)</t>
-        </is>
-      </c>
-      <c r="C14" s="18" t="inlineStr">
-        <is>
-          <t>5 | 2166呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>3 | 2133呎 (4+房)
-$15,380万
-$72,105/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="inlineStr">
-        <is>
-          <t>5 | 2166呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="inlineStr">
-        <is>
-          <t>3 | 2193呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C16" s="18" t="inlineStr">
-        <is>
-          <t>5 | 2166呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>3 | 2133呎 (4+房)
-$14,800万
-$69,386/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="inlineStr">
-        <is>
-          <t>5 | 2166呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t>3 | 2193呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C18" s="18" t="inlineStr">
-        <is>
-          <t>5 | 2166呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>3 | 2193呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C19" s="18" t="inlineStr">
-        <is>
-          <t>5 | 2166呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>3 | 2193呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="inlineStr">
-        <is>
-          <t>5 | 2166呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B21" s="18" t="inlineStr">
-        <is>
-          <t>3 | 2193呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C21" s="18" t="inlineStr">
-        <is>
-          <t>5 | 2166呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B22" s="18" t="inlineStr">
-        <is>
-          <t>3 | 2193呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C22" s="18" t="inlineStr">
-        <is>
-          <t>5 | 2166呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B23" s="18" t="inlineStr">
-        <is>
-          <t>3 | 2193呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C23" s="18" t="inlineStr">
-        <is>
-          <t>5 | 2166呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B24" s="18" t="inlineStr">
-        <is>
-          <t>3 | 2193呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C24" s="18" t="inlineStr">
-        <is>
-          <t>5 | 2166呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>1/F</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="inlineStr">
-        <is>
-          <t>3 | 2065呎 (4+房)
-$12,695万
-$61,477/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="C25" s="16" t="inlineStr">
-        <is>
-          <t>5 | 2029呎 (4+房)
-$12,560万
-$61,902/呎
-(25年-10月)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>21 Borrett Road 第1期 - 6号及7号 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>39 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>26 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>13 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>6 | 2927呎 (4+房)
-$37,737万
-$128,927/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>6 | 2112呎 (4+房)
-$18,150万
-$85,938/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>7 | 2256呎 (4+房)
-$20,850万
-$92,420/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>6 | 2112呎 (4+房)
-$19,011万
-$90,014/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>7 | 2256呎 (4+房)
-$20,389万
-$90,376/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B9" s="18" t="inlineStr">
-        <is>
-          <t>6 | 2169呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="18" t="inlineStr">
-        <is>
-          <t>7 | 2316呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>6 | 2112呎 (4+房)
-$17,200万
-$81,439/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>7 | 2256呎 (4+房)
-$19,038万
-$84,388/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>6 | 2112呎 (4+房)
-$16,680万
-$78,977/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>7 | 2256呎 (4+房)
-$18,523万
-$82,107/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>6 | 2169呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>7 | 2256呎 (4+房)
-$18,000万
-$79,787/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>6 | 2112呎 (4+房)
-$15,930万
-$75,426/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>7 | 2256呎 (4+房)
-$17,360万
-$76,950/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>6 | 2112呎 (4+房)
-$15,480万
-$73,295/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>7 | 2256呎 (4+房)
-$16,800万
-$74,468/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>6 | 2112呎 (4+房)
-$14,000万
-$66,288/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="inlineStr">
-        <is>
-          <t>7 | 2316呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="inlineStr">
-        <is>
-          <t>6 | 2169呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>7 | 2256呎 (4+房)
-$16,280万
-$72,163/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>6 | 2112呎 (4+房)
-$14,400万
-$68,182/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>7 | 2256呎 (4+房)
-$15,280万
-$67,730/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>6 | 2112呎 (4+房)
-$13,600万
-$64,394/呎
-(23年-12月)</t>
-        </is>
-      </c>
-      <c r="C18" s="18" t="inlineStr">
-        <is>
-          <t>7 | 2316呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>6 | 2169呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C19" s="18" t="inlineStr">
-        <is>
-          <t>7 | 2316呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
-        <is>
-          <t>6 | 2112呎 (4+房)
-$13,080万
-$61,932/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>7 | 2256呎 (4+房)
-$14,420万
-$63,918/呎
-(26年-07月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B21" s="18" t="inlineStr">
-        <is>
-          <t>6 | 2169呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C21" s="18" t="inlineStr">
-        <is>
-          <t>7 | 2316呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
-        <is>
-          <t>6 | 2112呎 (4+房)
-$11,700万
-$55,398/呎
-(24年-07月)</t>
-        </is>
-      </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>7 | 2256呎 (4+房)
-$13,842万
-$61,357/呎
-(26年-01月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="inlineStr">
-        <is>
-          <t>6 | 2112呎 (4+房)
-$11,500万
-$54,451/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="C23" s="18" t="inlineStr">
-        <is>
-          <t>7 | 2316呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B24" s="18" t="inlineStr">
-        <is>
-          <t>6 | 2169呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C24" s="18" t="inlineStr">
-        <is>
-          <t>7 | 2316呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>1/F</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="inlineStr">
-        <is>
-          <t>6 | 2032呎 (4+房)
-$12,630万
-$62,156/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="C25" s="16" t="inlineStr">
-        <is>
-          <t>7 | 2176呎 (4+房)
-$15,430万
-$70,910/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/港岛-半山区西部-21 Borrett Road 第1期.xlsx
+++ b/files/港岛-半山区西部-21 Borrett Road 第1期.xlsx
@@ -8,6 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1号及2号" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3号及5号" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6号及7号" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +44,90 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +138,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +203,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +219,57 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +646,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -6121,4 +6293,1673 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>1号及2号 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>1 | 3309呎 (4+房)
+$45941万
+$138,836/呎
+(21年-03月)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>1 | 2945呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>2 | 2154呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>1 | 2945呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>2 | 2154呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>1 | 2886呎 (4+房)
+$27063万
+$93,775/呎
+(22年-06月)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>2 | 2096呎 (4+房)
+$18080万
+$86,260/呎
+(23年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>1 | 2886呎 (4+房)
+$25000万
+$86,625/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>2 | 2096呎 (4+房)
+$16952万
+$80,878/呎
+(21年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>1 | 2945呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>2 | 2096呎 (4+房)
+$17000万
+$81,107/呎
+(21年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>1 | 2945呎 (4+房)
+$23854万
+$81,000/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>2 | 2096呎 (4+房)
+$16000万
+$76,336/呎
+(21年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>1 | 2886呎 (4+房)
+$23280万
+$80,665/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>2 | 2096呎 (4+房)
+$15500万
+$73,950/呎
+(21年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>1 | 2886呎 (4+房)
+$23146万
+$80,201/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>2 | 2154呎 (4+房)
+$15078万
+$70,000/呎
+(21年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>1 | 2886呎 (4+房)
+$22971万
+$79,595/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>2 | 2096呎 (4+房)
+$14550万
+$69,418/呎
+(23年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>1 | 2886呎 (4+房)
+$21035万
+$72,885/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>2 | 2096呎 (4+房)
+$13600万
+$64,885/呎
+(24年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>1 | 2886呎 (4+房)
+$21800万
+$75,537/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>2 | 2154呎 (4+房)
+$13300万
+$61,746/呎
+(22年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>1 | 2945呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>2 | 2154呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>1 | 2945呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>2 | 2154呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>1 | 2945呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>2 | 2154呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>1 | 2945呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>2 | 2154呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>1 | 2945呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>2 | 2154呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>1 | 2945呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>2 | 2154呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>1 | 2876呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>2 | 2075呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>3号及5号 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>3 | 2664呎 (4+房)
+$34411万
+$129,169/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>3 | 2133呎 (4+房)
+$20000万
+$93,765/呎
+(21年-11月)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>5 | 2109呎 (4+房)
+$18600万
+$88,193/呎
+(21年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>3 | 2193呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>5 | 2166呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>3 | 2193呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>5 | 2166呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>3 | 2133呎 (4+房)
+$17680万
+$82,888/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>5 | 2166呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>3 | 2133呎 (4+房)
+$17200万
+$80,638/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>5 | 2166呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>3 | 2133呎 (4+房)
+$16780万
+$78,669/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>5 | 2166呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>3 | 2133呎 (4+房)
+$16200万
+$75,949/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>5 | 2166呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>3 | 2133呎 (4+房)
+$15600万
+$73,136/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>5 | 2166呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>3 | 2133呎 (4+房)
+$15380万
+$72,105/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>5 | 2166呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>3 | 2193呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>5 | 2166呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>3 | 2133呎 (4+房)
+$14800万
+$69,386/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>5 | 2166呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>3 | 2193呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>5 | 2166呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>3 | 2193呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>5 | 2166呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>3 | 2193呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>5 | 2166呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>3 | 2193呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>5 | 2166呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>3 | 2193呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>5 | 2166呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>3 | 2193呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>5 | 2166呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>3 | 2193呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>5 | 2166呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>3 | 2065呎 (4+房)
+$12695万
+$61,477/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>5 | 2029呎 (4+房)
+$12560万
+$61,902/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>6号及7号 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>6 | 2927呎 (4+房)
+$37737万
+$128,927/呎
+(21年-04月)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>6 | 2112呎 (4+房)
+$18150万
+$85,938/呎
+(21年-08月)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>7 | 2256呎 (4+房)
+$20850万
+$92,420/呎
+(21年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>6 | 2112呎 (4+房)
+$19011万
+$90,014/呎
+(22年-06月)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>7 | 2256呎 (4+房)
+$20389万
+$90,376/呎
+(22年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>6 | 2169呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>7 | 2316呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>6 | 2112呎 (4+房)
+$17200万
+$81,439/呎
+(21年-11月)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>7 | 2256呎 (4+房)
+$19038万
+$84,388/呎
+(21年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>6 | 2112呎 (4+房)
+$16680万
+$78,977/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>7 | 2256呎 (4+房)
+$18523万
+$82,107/呎
+(21年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>6 | 2169呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>7 | 2256呎 (4+房)
+$18000万
+$79,787/呎
+(21年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>6 | 2112呎 (4+房)
+$15930万
+$75,426/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>7 | 2256呎 (4+房)
+$17360万
+$76,950/呎
+(21年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>6 | 2112呎 (4+房)
+$15480万
+$73,295/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>7 | 2256呎 (4+房)
+$16800万
+$74,468/呎
+(21年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>6 | 2112呎 (4+房)
+$14000万
+$66,288/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>7 | 2316呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>6 | 2169呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>7 | 2256呎 (4+房)
+$16280万
+$72,163/呎
+(23年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>6 | 2112呎 (4+房)
+$14400万
+$68,182/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>7 | 2256呎 (4+房)
+$15280万
+$67,730/呎
+(23年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>6 | 2112呎 (4+房)
+$13600万
+$64,394/呎
+(23年-12月)</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>7 | 2316呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>6 | 2169呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>7 | 2316呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>6 | 2112呎 (4+房)
+$13080万
+$61,932/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>7 | 2256呎 (4+房)
+$14420万
+$63,918/呎
+(26年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>6 | 2169呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>7 | 2316呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>6 | 2112呎 (4+房)
+$11700万
+$55,398/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>7 | 2256呎 (4+房)
+$13842万
+$61,357/呎
+(26年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>6 | 2112呎 (4+房)
+$11500万
+$54,451/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>7 | 2316呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>6 | 2169呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>7 | 2316呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>6 | 2032呎 (4+房)
+$12630万
+$62,156/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>7 | 2176呎 (4+房)
+$15430万
+$70,910/呎
+(21年-10月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/港岛-半山区西部-21 Borrett Road 第1期.xlsx
+++ b/files/港岛-半山区西部-21 Borrett Road 第1期.xlsx
@@ -646,7 +646,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>

--- a/files/港岛-半山区西部-21 Borrett Road 第1期.xlsx
+++ b/files/港岛-半山区西部-21 Borrett Road 第1期.xlsx
@@ -636,7 +636,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J118"/>
+  <dimension ref="A1:N118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
@@ -649,6 +649,10 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -706,6 +710,26 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>最高折扣</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>折实总价 (港币)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>折实呎价 (港币/呎)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>付款办法</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>是否招标</t>
         </is>
       </c>
@@ -752,6 +776,26 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -802,6 +846,26 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -852,6 +916,26 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -902,6 +986,26 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -952,6 +1056,26 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -998,6 +1122,26 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1044,6 +1188,26 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1090,6 +1254,26 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1136,6 +1320,26 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1182,6 +1386,26 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1232,6 +1456,26 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1278,6 +1522,26 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1324,6 +1588,26 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1370,6 +1654,26 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1416,6 +1720,26 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1462,6 +1786,26 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1508,6 +1852,26 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1554,6 +1918,26 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1600,6 +1984,26 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1646,6 +2050,26 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1692,6 +2116,26 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1738,6 +2182,26 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1788,6 +2252,26 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1834,6 +2318,26 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1884,6 +2388,26 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1934,6 +2458,26 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1984,6 +2528,26 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2034,6 +2598,26 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2084,6 +2668,26 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2134,6 +2738,26 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2184,6 +2808,26 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2234,6 +2878,26 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2284,6 +2948,26 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2334,6 +3018,26 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2384,6 +3088,26 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2434,6 +3158,26 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2484,6 +3228,26 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2534,6 +3298,26 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2580,6 +3364,26 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2626,6 +3430,26 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2672,6 +3496,26 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2722,6 +3566,26 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2772,6 +3636,26 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2822,6 +3706,26 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2872,6 +3776,26 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2922,6 +3846,26 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2968,6 +3912,26 @@
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3018,6 +3982,26 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3064,6 +4048,26 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L51" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3114,6 +4118,26 @@
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3160,6 +4184,26 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L53" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3210,6 +4254,26 @@
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3256,6 +4320,26 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K55" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L55" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3306,6 +4390,26 @@
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L56" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3352,6 +4456,26 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K57" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L57" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N57" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3402,6 +4526,26 @@
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3448,6 +4592,26 @@
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K59" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L59" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3498,6 +4662,26 @@
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K60" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L60" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N60" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3548,6 +4732,26 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K61" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L61" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N61" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3598,6 +4802,26 @@
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K62" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L62" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N62" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3644,6 +4868,26 @@
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K63" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L63" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N63" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3694,6 +4938,26 @@
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L64" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N64" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3744,6 +5008,26 @@
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K65" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L65" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M65" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N65" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3794,6 +5078,26 @@
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K66" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L66" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N66" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3844,6 +5148,26 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K67" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L67" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M67" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N67" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3894,6 +5218,26 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K68" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L68" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N68" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3944,6 +5288,26 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K69" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L69" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M69" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N69" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3994,6 +5358,26 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K70" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L70" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N70" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4044,6 +5428,26 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K71" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L71" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M71" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N71" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4094,6 +5498,26 @@
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K72" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L72" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M72" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N72" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4144,6 +5568,26 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K73" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L73" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M73" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N73" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4194,6 +5638,26 @@
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K74" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L74" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M74" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N74" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4244,6 +5708,26 @@
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K75" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L75" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M75" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N75" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4294,6 +5778,26 @@
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K76" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L76" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M76" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N76" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4344,6 +5848,26 @@
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K77" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L77" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M77" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N77" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4390,6 +5914,26 @@
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K78" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L78" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M78" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N78" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4436,6 +5980,26 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K79" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L79" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M79" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N79" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4482,6 +6046,26 @@
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K80" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L80" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M80" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N80" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4528,6 +6112,26 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K81" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L81" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M81" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N81" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4574,6 +6178,26 @@
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K82" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L82" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M82" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N82" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4620,6 +6244,26 @@
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K83" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L83" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M83" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N83" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4666,6 +6310,26 @@
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K84" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L84" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M84" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N84" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4716,6 +6380,26 @@
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K85" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L85" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M85" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N85" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4766,6 +6450,26 @@
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K86" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L86" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M86" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N86" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4812,6 +6516,26 @@
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K87" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L87" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M87" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N87" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4858,6 +6582,26 @@
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K88" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L88" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M88" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N88" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4904,6 +6648,26 @@
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K89" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L89" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M89" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N89" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4950,6 +6714,26 @@
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K90" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L90" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M90" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N90" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4996,6 +6780,26 @@
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K91" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L91" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M91" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N91" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5046,6 +6850,26 @@
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K92" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L92" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M92" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N92" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5092,6 +6916,26 @@
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K93" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L93" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M93" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N93" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5138,6 +6982,26 @@
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K94" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L94" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M94" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N94" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5184,6 +7048,26 @@
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K95" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L95" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M95" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N95" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5230,6 +7114,26 @@
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K96" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L96" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M96" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N96" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5280,6 +7184,26 @@
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K97" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L97" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M97" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N97" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5326,6 +7250,26 @@
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K98" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L98" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M98" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N98" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5372,6 +7316,26 @@
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K99" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L99" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M99" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N99" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5422,6 +7386,26 @@
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K100" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L100" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M100" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N100" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5468,6 +7452,26 @@
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K101" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L101" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M101" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N101" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5514,6 +7518,26 @@
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K102" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L102" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M102" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N102" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5564,6 +7588,26 @@
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K103" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L103" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M103" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N103" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5610,6 +7654,26 @@
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K104" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L104" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M104" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N104" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5660,6 +7724,26 @@
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K105" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L105" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M105" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N105" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5710,6 +7794,26 @@
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K106" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L106" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M106" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N106" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5756,6 +7860,26 @@
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K107" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L107" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M107" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N107" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5802,6 +7926,26 @@
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K108" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L108" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M108" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N108" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5852,6 +7996,26 @@
       </c>
       <c r="J109" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K109" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L109" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M109" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N109" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5902,6 +8066,26 @@
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K110" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L110" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M110" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N110" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5948,6 +8132,26 @@
       </c>
       <c r="J111" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K111" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L111" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M111" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N111" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5994,6 +8198,26 @@
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K112" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L112" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M112" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N112" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6044,6 +8268,26 @@
       </c>
       <c r="J113" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K113" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L113" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M113" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N113" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6090,6 +8334,26 @@
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K114" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L114" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M114" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N114" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6140,6 +8404,26 @@
       </c>
       <c r="J115" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K115" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L115" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M115" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N115" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6190,6 +8474,26 @@
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K116" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L116" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M116" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N116" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6236,6 +8540,26 @@
       </c>
       <c r="J117" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K117" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L117" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M117" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N117" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6282,13 +8606,33 @@
       </c>
       <c r="J118" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K118" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L118" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M118" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N118" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -6408,7 +8752,7 @@
           <t>1 | 3309呎 (4+房)
 $45941万
 $138,836/呎
-(21年-03月)</t>
+(21年-03月-02日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -6470,7 +8814,7 @@
           <t>1 | 2886呎 (4+房)
 $27063万
 $93,775/呎
-(22年-06月)</t>
+(22年-06月-22日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -6478,7 +8822,7 @@
           <t>2 | 2096呎 (4+房)
 $18080万
 $86,260/呎
-(23年-10月)</t>
+(23年-10月-24日)</t>
         </is>
       </c>
     </row>
@@ -6493,7 +8837,7 @@
           <t>1 | 2886呎 (4+房)
 $25000万
 $86,625/呎
-(21年-05月)</t>
+(21年-05月-27日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -6501,7 +8845,7 @@
           <t>2 | 2096呎 (4+房)
 $16952万
 $80,878/呎
-(21年-07月)</t>
+(21年-07月-15日)</t>
         </is>
       </c>
     </row>
@@ -6524,7 +8868,7 @@
           <t>2 | 2096呎 (4+房)
 $17000万
 $81,107/呎
-(21年-05月)</t>
+(21年-05月-27日)</t>
         </is>
       </c>
     </row>
@@ -6539,7 +8883,7 @@
           <t>1 | 2945呎 (4+房)
 $23854万
 $81,000/呎
-(21年-07月)</t>
+(21年-07月-01日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -6547,7 +8891,7 @@
           <t>2 | 2096呎 (4+房)
 $16000万
 $76,336/呎
-(21年-09月)</t>
+(21年-09月-29日)</t>
         </is>
       </c>
     </row>
@@ -6562,7 +8906,7 @@
           <t>1 | 2886呎 (4+房)
 $23280万
 $80,665/呎
-(21年-06月)</t>
+(21年-06月-01日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -6570,7 +8914,7 @@
           <t>2 | 2096呎 (4+房)
 $15500万
 $73,950/呎
-(21年-07月)</t>
+(21年-07月-05日)</t>
         </is>
       </c>
     </row>
@@ -6585,7 +8929,7 @@
           <t>1 | 2886呎 (4+房)
 $23146万
 $80,201/呎
-(21年-06月)</t>
+(21年-06月-24日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -6593,7 +8937,7 @@
           <t>2 | 2154呎 (4+房)
 $15078万
 $70,000/呎
-(21年-04月)</t>
+(21年-04月-14日)</t>
         </is>
       </c>
     </row>
@@ -6608,7 +8952,7 @@
           <t>1 | 2886呎 (4+房)
 $22971万
 $79,595/呎
-(21年-07月)</t>
+(21年-07月-05日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -6616,7 +8960,7 @@
           <t>2 | 2096呎 (4+房)
 $14550万
 $69,418/呎
-(23年-03月)</t>
+(23年-03月-23日)</t>
         </is>
       </c>
     </row>
@@ -6631,7 +8975,7 @@
           <t>1 | 2886呎 (4+房)
 $21035万
 $72,885/呎
-(26年-02月)</t>
+(26年-02月-04日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -6639,7 +8983,7 @@
           <t>2 | 2096呎 (4+房)
 $13600万
 $64,885/呎
-(24年-11月)</t>
+(24年-11月-28日)</t>
         </is>
       </c>
     </row>
@@ -6654,7 +8998,7 @@
           <t>1 | 2886呎 (4+房)
 $21800万
 $75,537/呎
-(24年-04月)</t>
+(24年-04月-28日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -6662,7 +9006,7 @@
           <t>2 | 2154呎 (4+房)
 $13300万
 $61,746/呎
-(22年-11月)</t>
+(22年-11月-15日)</t>
         </is>
       </c>
     </row>
@@ -6949,7 +9293,7 @@
           <t>3 | 2664呎 (4+房)
 $34411万
 $129,169/呎
-(21年-05月)</t>
+(21年-05月-10日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -6965,7 +9309,7 @@
           <t>3 | 2133呎 (4+房)
 $20000万
 $93,765/呎
-(21年-11月)</t>
+(21年-11月-23日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -6973,7 +9317,7 @@
           <t>5 | 2109呎 (4+房)
 $18600万
 $88,193/呎
-(21年-11月)</t>
+(21年-11月-23日)</t>
         </is>
       </c>
     </row>
@@ -7034,7 +9378,7 @@
           <t>3 | 2133呎 (4+房)
 $17680万
 $82,888/呎
-(22年-01月)</t>
+(22年-01月-06日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -7057,7 +9401,7 @@
           <t>3 | 2133呎 (4+房)
 $17200万
 $80,638/呎
-(21年-06月)</t>
+(21年-06月-29日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -7080,7 +9424,7 @@
           <t>3 | 2133呎 (4+房)
 $16780万
 $78,669/呎
-(22年-02月)</t>
+(22年-02月-28日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -7103,7 +9447,7 @@
           <t>3 | 2133呎 (4+房)
 $16200万
 $75,949/呎
-(25年-08月)</t>
+(25年-08月-20日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -7126,7 +9470,7 @@
           <t>3 | 2133呎 (4+房)
 $15600万
 $73,136/呎
-(24年-12月)</t>
+(24年-12月-09日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -7149,7 +9493,7 @@
           <t>3 | 2133呎 (4+房)
 $15380万
 $72,105/呎
-(23年-05月)</t>
+(23年-05月-04日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -7195,7 +9539,7 @@
           <t>3 | 2133呎 (4+房)
 $14800万
 $69,386/呎
-(25年-06月)</t>
+(25年-06月-18日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -7379,7 +9723,7 @@
           <t>3 | 2065呎 (4+房)
 $12695万
 $61,477/呎
-(25年-04月)</t>
+(25年-04月-24日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -7387,7 +9731,7 @@
           <t>5 | 2029呎 (4+房)
 $12560万
 $61,902/呎
-(25年-10月)</t>
+(25年-10月-02日)</t>
         </is>
       </c>
     </row>
@@ -7513,7 +9857,7 @@
           <t>6 | 2927呎 (4+房)
 $37737万
 $128,927/呎
-(21年-04月)</t>
+(21年-04月-15日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -7529,7 +9873,7 @@
           <t>6 | 2112呎 (4+房)
 $18150万
 $85,938/呎
-(21年-08月)</t>
+(21年-08月-02日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -7537,7 +9881,7 @@
           <t>7 | 2256呎 (4+房)
 $20850万
 $92,420/呎
-(21年-08月)</t>
+(21年-08月-02日)</t>
         </is>
       </c>
     </row>
@@ -7552,7 +9896,7 @@
           <t>6 | 2112呎 (4+房)
 $19011万
 $90,014/呎
-(22年-06月)</t>
+(22年-06月-01日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -7560,7 +9904,7 @@
           <t>7 | 2256呎 (4+房)
 $20389万
 $90,376/呎
-(22年-06月)</t>
+(22年-06月-01日)</t>
         </is>
       </c>
     </row>
@@ -7598,7 +9942,7 @@
           <t>6 | 2112呎 (4+房)
 $17200万
 $81,439/呎
-(21年-11月)</t>
+(21年-11月-15日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -7606,7 +9950,7 @@
           <t>7 | 2256呎 (4+房)
 $19038万
 $84,388/呎
-(21年-08月)</t>
+(21年-08月-15日)</t>
         </is>
       </c>
     </row>
@@ -7621,7 +9965,7 @@
           <t>6 | 2112呎 (4+房)
 $16680万
 $78,977/呎
-(22年-01月)</t>
+(22年-01月-30日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -7629,7 +9973,7 @@
           <t>7 | 2256呎 (4+房)
 $18523万
 $82,107/呎
-(21年-10月)</t>
+(21年-10月-20日)</t>
         </is>
       </c>
     </row>
@@ -7652,7 +9996,7 @@
           <t>7 | 2256呎 (4+房)
 $18000万
 $79,787/呎
-(21年-10月)</t>
+(21年-10月-18日)</t>
         </is>
       </c>
     </row>
@@ -7667,7 +10011,7 @@
           <t>6 | 2112呎 (4+房)
 $15930万
 $75,426/呎
-(21年-10月)</t>
+(21年-10月-11日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -7675,7 +10019,7 @@
           <t>7 | 2256呎 (4+房)
 $17360万
 $76,950/呎
-(21年-10月)</t>
+(21年-10月-18日)</t>
         </is>
       </c>
     </row>
@@ -7690,7 +10034,7 @@
           <t>6 | 2112呎 (4+房)
 $15480万
 $73,295/呎
-(21年-09月)</t>
+(21年-09月-09日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -7698,7 +10042,7 @@
           <t>7 | 2256呎 (4+房)
 $16800万
 $74,468/呎
-(21年-04月)</t>
+(21年-04月-26日)</t>
         </is>
       </c>
     </row>
@@ -7713,7 +10057,7 @@
           <t>6 | 2112呎 (4+房)
 $14000万
 $66,288/呎
-(24年-05月)</t>
+(24年-05月-29日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -7744,7 +10088,7 @@
           <t>7 | 2256呎 (4+房)
 $16280万
 $72,163/呎
-(23年-04月)</t>
+(23年-04月-02日)</t>
         </is>
       </c>
     </row>
@@ -7759,7 +10103,7 @@
           <t>6 | 2112呎 (4+房)
 $14400万
 $68,182/呎
-(25年-09月)</t>
+(25年-09月-01日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -7767,7 +10111,7 @@
           <t>7 | 2256呎 (4+房)
 $15280万
 $67,730/呎
-(23年-03月)</t>
+(23年-03月-20日)</t>
         </is>
       </c>
     </row>
@@ -7782,7 +10126,7 @@
           <t>6 | 2112呎 (4+房)
 $13600万
 $64,394/呎
-(23年-12月)</t>
+(23年-12月-11日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -7828,7 +10172,7 @@
           <t>6 | 2112呎 (4+房)
 $13080万
 $61,932/呎
-(26年-07月)</t>
+(26年-07月-05日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -7836,7 +10180,7 @@
           <t>7 | 2256呎 (4+房)
 $14420万
 $63,918/呎
-(26年-07月)</t>
+(26年-07月-05日)</t>
         </is>
       </c>
     </row>
@@ -7874,7 +10218,7 @@
           <t>6 | 2112呎 (4+房)
 $11700万
 $55,398/呎
-(24年-07月)</t>
+(24年-07月-11日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -7882,7 +10226,7 @@
           <t>7 | 2256呎 (4+房)
 $13842万
 $61,357/呎
-(26年-01月)</t>
+(26年-01月-25日)</t>
         </is>
       </c>
     </row>
@@ -7897,7 +10241,7 @@
           <t>6 | 2112呎 (4+房)
 $11500万
 $54,451/呎
-(24年-06月)</t>
+(24年-06月-11日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -7943,7 +10287,7 @@
           <t>6 | 2032呎 (4+房)
 $12630万
 $62,156/呎
-(25年-03月)</t>
+(25年-03月-13日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -7951,7 +10295,7 @@
           <t>7 | 2176呎 (4+房)
 $15430万
 $70,910/呎
-(21年-10月)</t>
+(21年-10月-21日)</t>
         </is>
       </c>
     </row>

--- a/files/港岛-半山区西部-21 Borrett Road 第1期.xlsx
+++ b/files/港岛-半山区西部-21 Borrett Road 第1期.xlsx
@@ -22,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -126,6 +126,12 @@
       <color rgb="007F7F7F"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -203,7 +209,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -269,6 +275,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -7704,7 +7713,7 @@
       </c>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G105" s="3" t="inlineStr">
@@ -7714,12 +7723,12 @@
       </c>
       <c r="H105" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I105" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J105" s="3" t="inlineStr">
@@ -7729,12 +7738,12 @@
       </c>
       <c r="K105" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L105" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M105" s="3" t="inlineStr">
@@ -7744,7 +7753,7 @@
       </c>
       <c r="N105" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -9805,27 +9814,27 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
     </row>
@@ -10152,12 +10161,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C18" s="22" t="inlineStr">
+      <c r="C18" s="23" t="inlineStr">
         <is>
           <t>7 | 2316呎 (4+房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
     </row>

--- a/files/港岛-半山区西部-21 Borrett Road 第1期.xlsx
+++ b/files/港岛-半山区西部-21 Borrett Road 第1期.xlsx
@@ -8761,7 +8761,7 @@
           <t>1 | 3309呎 (4+房)
 $45941万
 $138,836/呎
-(21年-03月-02日)</t>
+(21年-03月)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -8823,7 +8823,7 @@
           <t>1 | 2886呎 (4+房)
 $27063万
 $93,775/呎
-(22年-06月-22日)</t>
+(22年-06月)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -8831,7 +8831,7 @@
           <t>2 | 2096呎 (4+房)
 $18080万
 $86,260/呎
-(23年-10月-24日)</t>
+(23年-10月)</t>
         </is>
       </c>
     </row>
@@ -8846,7 +8846,7 @@
           <t>1 | 2886呎 (4+房)
 $25000万
 $86,625/呎
-(21年-05月-27日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -8854,7 +8854,7 @@
           <t>2 | 2096呎 (4+房)
 $16952万
 $80,878/呎
-(21年-07月-15日)</t>
+(21年-07月)</t>
         </is>
       </c>
     </row>
@@ -8877,7 +8877,7 @@
           <t>2 | 2096呎 (4+房)
 $17000万
 $81,107/呎
-(21年-05月-27日)</t>
+(21年-05月)</t>
         </is>
       </c>
     </row>
@@ -8892,7 +8892,7 @@
           <t>1 | 2945呎 (4+房)
 $23854万
 $81,000/呎
-(21年-07月-01日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -8900,7 +8900,7 @@
           <t>2 | 2096呎 (4+房)
 $16000万
 $76,336/呎
-(21年-09月-29日)</t>
+(21年-09月)</t>
         </is>
       </c>
     </row>
@@ -8915,7 +8915,7 @@
           <t>1 | 2886呎 (4+房)
 $23280万
 $80,665/呎
-(21年-06月-01日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -8923,7 +8923,7 @@
           <t>2 | 2096呎 (4+房)
 $15500万
 $73,950/呎
-(21年-07月-05日)</t>
+(21年-07月)</t>
         </is>
       </c>
     </row>
@@ -8938,7 +8938,7 @@
           <t>1 | 2886呎 (4+房)
 $23146万
 $80,201/呎
-(21年-06月-24日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -8946,7 +8946,7 @@
           <t>2 | 2154呎 (4+房)
 $15078万
 $70,000/呎
-(21年-04月-14日)</t>
+(21年-04月)</t>
         </is>
       </c>
     </row>
@@ -8961,7 +8961,7 @@
           <t>1 | 2886呎 (4+房)
 $22971万
 $79,595/呎
-(21年-07月-05日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -8969,7 +8969,7 @@
           <t>2 | 2096呎 (4+房)
 $14550万
 $69,418/呎
-(23年-03月-23日)</t>
+(23年-03月)</t>
         </is>
       </c>
     </row>
@@ -8984,7 +8984,7 @@
           <t>1 | 2886呎 (4+房)
 $21035万
 $72,885/呎
-(26年-02月-04日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -8992,7 +8992,7 @@
           <t>2 | 2096呎 (4+房)
 $13600万
 $64,885/呎
-(24年-11月-28日)</t>
+(24年-11月)</t>
         </is>
       </c>
     </row>
@@ -9007,7 +9007,7 @@
           <t>1 | 2886呎 (4+房)
 $21800万
 $75,537/呎
-(24年-04月-28日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -9015,7 +9015,7 @@
           <t>2 | 2154呎 (4+房)
 $13300万
 $61,746/呎
-(22年-11月-15日)</t>
+(22年-11月)</t>
         </is>
       </c>
     </row>
@@ -9302,7 +9302,7 @@
           <t>3 | 2664呎 (4+房)
 $34411万
 $129,169/呎
-(21年-05月-10日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -9318,7 +9318,7 @@
           <t>3 | 2133呎 (4+房)
 $20000万
 $93,765/呎
-(21年-11月-23日)</t>
+(21年-11月)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -9326,7 +9326,7 @@
           <t>5 | 2109呎 (4+房)
 $18600万
 $88,193/呎
-(21年-11月-23日)</t>
+(21年-11月)</t>
         </is>
       </c>
     </row>
@@ -9387,7 +9387,7 @@
           <t>3 | 2133呎 (4+房)
 $17680万
 $82,888/呎
-(22年-01月-06日)</t>
+(22年-01月)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -9410,7 +9410,7 @@
           <t>3 | 2133呎 (4+房)
 $17200万
 $80,638/呎
-(21年-06月-29日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -9433,7 +9433,7 @@
           <t>3 | 2133呎 (4+房)
 $16780万
 $78,669/呎
-(22年-02月-28日)</t>
+(22年-02月)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -9456,7 +9456,7 @@
           <t>3 | 2133呎 (4+房)
 $16200万
 $75,949/呎
-(25年-08月-20日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -9479,7 +9479,7 @@
           <t>3 | 2133呎 (4+房)
 $15600万
 $73,136/呎
-(24年-12月-09日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -9502,7 +9502,7 @@
           <t>3 | 2133呎 (4+房)
 $15380万
 $72,105/呎
-(23年-05月-04日)</t>
+(23年-05月)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -9548,7 +9548,7 @@
           <t>3 | 2133呎 (4+房)
 $14800万
 $69,386/呎
-(25年-06月-18日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -9732,7 +9732,7 @@
           <t>3 | 2065呎 (4+房)
 $12695万
 $61,477/呎
-(25年-04月-24日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -9740,7 +9740,7 @@
           <t>5 | 2029呎 (4+房)
 $12560万
 $61,902/呎
-(25年-10月-02日)</t>
+(25年-10月)</t>
         </is>
       </c>
     </row>
@@ -9866,7 +9866,7 @@
           <t>6 | 2927呎 (4+房)
 $37737万
 $128,927/呎
-(21年-04月-15日)</t>
+(21年-04月)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -9882,7 +9882,7 @@
           <t>6 | 2112呎 (4+房)
 $18150万
 $85,938/呎
-(21年-08月-02日)</t>
+(21年-08月)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -9890,7 +9890,7 @@
           <t>7 | 2256呎 (4+房)
 $20850万
 $92,420/呎
-(21年-08月-02日)</t>
+(21年-08月)</t>
         </is>
       </c>
     </row>
@@ -9905,7 +9905,7 @@
           <t>6 | 2112呎 (4+房)
 $19011万
 $90,014/呎
-(22年-06月-01日)</t>
+(22年-06月)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -9913,7 +9913,7 @@
           <t>7 | 2256呎 (4+房)
 $20389万
 $90,376/呎
-(22年-06月-01日)</t>
+(22年-06月)</t>
         </is>
       </c>
     </row>
@@ -9951,7 +9951,7 @@
           <t>6 | 2112呎 (4+房)
 $17200万
 $81,439/呎
-(21年-11月-15日)</t>
+(21年-11月)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -9959,7 +9959,7 @@
           <t>7 | 2256呎 (4+房)
 $19038万
 $84,388/呎
-(21年-08月-15日)</t>
+(21年-08月)</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
           <t>6 | 2112呎 (4+房)
 $16680万
 $78,977/呎
-(22年-01月-30日)</t>
+(22年-01月)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -9982,7 +9982,7 @@
           <t>7 | 2256呎 (4+房)
 $18523万
 $82,107/呎
-(21年-10月-20日)</t>
+(21年-10月)</t>
         </is>
       </c>
     </row>
@@ -10005,7 +10005,7 @@
           <t>7 | 2256呎 (4+房)
 $18000万
 $79,787/呎
-(21年-10月-18日)</t>
+(21年-10月)</t>
         </is>
       </c>
     </row>
@@ -10020,7 +10020,7 @@
           <t>6 | 2112呎 (4+房)
 $15930万
 $75,426/呎
-(21年-10月-11日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -10028,7 +10028,7 @@
           <t>7 | 2256呎 (4+房)
 $17360万
 $76,950/呎
-(21年-10月-18日)</t>
+(21年-10月)</t>
         </is>
       </c>
     </row>
@@ -10043,7 +10043,7 @@
           <t>6 | 2112呎 (4+房)
 $15480万
 $73,295/呎
-(21年-09月-09日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -10051,7 +10051,7 @@
           <t>7 | 2256呎 (4+房)
 $16800万
 $74,468/呎
-(21年-04月-26日)</t>
+(21年-04月)</t>
         </is>
       </c>
     </row>
@@ -10066,7 +10066,7 @@
           <t>6 | 2112呎 (4+房)
 $14000万
 $66,288/呎
-(24年-05月-29日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -10097,7 +10097,7 @@
           <t>7 | 2256呎 (4+房)
 $16280万
 $72,163/呎
-(23年-04月-02日)</t>
+(23年-04月)</t>
         </is>
       </c>
     </row>
@@ -10112,7 +10112,7 @@
           <t>6 | 2112呎 (4+房)
 $14400万
 $68,182/呎
-(25年-09月-01日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -10120,7 +10120,7 @@
           <t>7 | 2256呎 (4+房)
 $15280万
 $67,730/呎
-(23年-03月-20日)</t>
+(23年-03月)</t>
         </is>
       </c>
     </row>
@@ -10135,7 +10135,7 @@
           <t>6 | 2112呎 (4+房)
 $13600万
 $64,394/呎
-(23年-12月-11日)</t>
+(23年-12月)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -10181,7 +10181,7 @@
           <t>6 | 2112呎 (4+房)
 $13080万
 $61,932/呎
-(26年-07月-05日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -10189,7 +10189,7 @@
           <t>7 | 2256呎 (4+房)
 $14420万
 $63,918/呎
-(26年-07月-05日)</t>
+(26年-07月)</t>
         </is>
       </c>
     </row>
@@ -10227,7 +10227,7 @@
           <t>6 | 2112呎 (4+房)
 $11700万
 $55,398/呎
-(24年-07月-11日)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -10235,7 +10235,7 @@
           <t>7 | 2256呎 (4+房)
 $13842万
 $61,357/呎
-(26年-01月-25日)</t>
+(26年-01月)</t>
         </is>
       </c>
     </row>
@@ -10250,7 +10250,7 @@
           <t>6 | 2112呎 (4+房)
 $11500万
 $54,451/呎
-(24年-06月-11日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -10296,7 +10296,7 @@
           <t>6 | 2032呎 (4+房)
 $12630万
 $62,156/呎
-(25年-03月-13日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -10304,7 +10304,7 @@
           <t>7 | 2176呎 (4+房)
 $15430万
 $70,910/呎
-(21年-10月-21日)</t>
+(21年-10月)</t>
         </is>
       </c>
     </row>

--- a/files/港岛-半山区西部-21 Borrett Road 第1期.xlsx
+++ b/files/港岛-半山区西部-21 Borrett Road 第1期.xlsx
@@ -8761,7 +8761,7 @@
           <t>1 | 3309呎 (4+房)
 $45941万
 $138,836/呎
-(21年-03月)</t>
+(21年-03月-02日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -8823,7 +8823,7 @@
           <t>1 | 2886呎 (4+房)
 $27063万
 $93,775/呎
-(22年-06月)</t>
+(22年-06月-22日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -8831,7 +8831,7 @@
           <t>2 | 2096呎 (4+房)
 $18080万
 $86,260/呎
-(23年-10月)</t>
+(23年-10月-24日)</t>
         </is>
       </c>
     </row>
@@ -8846,7 +8846,7 @@
           <t>1 | 2886呎 (4+房)
 $25000万
 $86,625/呎
-(21年-05月)</t>
+(21年-05月-27日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -8854,7 +8854,7 @@
           <t>2 | 2096呎 (4+房)
 $16952万
 $80,878/呎
-(21年-07月)</t>
+(21年-07月-15日)</t>
         </is>
       </c>
     </row>
@@ -8877,7 +8877,7 @@
           <t>2 | 2096呎 (4+房)
 $17000万
 $81,107/呎
-(21年-05月)</t>
+(21年-05月-27日)</t>
         </is>
       </c>
     </row>
@@ -8892,7 +8892,7 @@
           <t>1 | 2945呎 (4+房)
 $23854万
 $81,000/呎
-(21年-07月)</t>
+(21年-07月-01日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -8900,7 +8900,7 @@
           <t>2 | 2096呎 (4+房)
 $16000万
 $76,336/呎
-(21年-09月)</t>
+(21年-09月-29日)</t>
         </is>
       </c>
     </row>
@@ -8915,7 +8915,7 @@
           <t>1 | 2886呎 (4+房)
 $23280万
 $80,665/呎
-(21年-06月)</t>
+(21年-06月-01日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -8923,7 +8923,7 @@
           <t>2 | 2096呎 (4+房)
 $15500万
 $73,950/呎
-(21年-07月)</t>
+(21年-07月-05日)</t>
         </is>
       </c>
     </row>
@@ -8938,7 +8938,7 @@
           <t>1 | 2886呎 (4+房)
 $23146万
 $80,201/呎
-(21年-06月)</t>
+(21年-06月-24日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -8946,7 +8946,7 @@
           <t>2 | 2154呎 (4+房)
 $15078万
 $70,000/呎
-(21年-04月)</t>
+(21年-04月-14日)</t>
         </is>
       </c>
     </row>
@@ -8961,7 +8961,7 @@
           <t>1 | 2886呎 (4+房)
 $22971万
 $79,595/呎
-(21年-07月)</t>
+(21年-07月-05日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -8969,7 +8969,7 @@
           <t>2 | 2096呎 (4+房)
 $14550万
 $69,418/呎
-(23年-03月)</t>
+(23年-03月-23日)</t>
         </is>
       </c>
     </row>
@@ -8984,7 +8984,7 @@
           <t>1 | 2886呎 (4+房)
 $21035万
 $72,885/呎
-(26年-02月)</t>
+(26年-02月-04日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -8992,7 +8992,7 @@
           <t>2 | 2096呎 (4+房)
 $13600万
 $64,885/呎
-(24年-11月)</t>
+(24年-11月-28日)</t>
         </is>
       </c>
     </row>
@@ -9007,7 +9007,7 @@
           <t>1 | 2886呎 (4+房)
 $21800万
 $75,537/呎
-(24年-04月)</t>
+(24年-04月-28日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -9015,7 +9015,7 @@
           <t>2 | 2154呎 (4+房)
 $13300万
 $61,746/呎
-(22年-11月)</t>
+(22年-11月-15日)</t>
         </is>
       </c>
     </row>
@@ -9302,7 +9302,7 @@
           <t>3 | 2664呎 (4+房)
 $34411万
 $129,169/呎
-(21年-05月)</t>
+(21年-05月-10日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -9318,7 +9318,7 @@
           <t>3 | 2133呎 (4+房)
 $20000万
 $93,765/呎
-(21年-11月)</t>
+(21年-11月-23日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -9326,7 +9326,7 @@
           <t>5 | 2109呎 (4+房)
 $18600万
 $88,193/呎
-(21年-11月)</t>
+(21年-11月-23日)</t>
         </is>
       </c>
     </row>
@@ -9387,7 +9387,7 @@
           <t>3 | 2133呎 (4+房)
 $17680万
 $82,888/呎
-(22年-01月)</t>
+(22年-01月-06日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -9410,7 +9410,7 @@
           <t>3 | 2133呎 (4+房)
 $17200万
 $80,638/呎
-(21年-06月)</t>
+(21年-06月-29日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -9433,7 +9433,7 @@
           <t>3 | 2133呎 (4+房)
 $16780万
 $78,669/呎
-(22年-02月)</t>
+(22年-02月-28日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -9456,7 +9456,7 @@
           <t>3 | 2133呎 (4+房)
 $16200万
 $75,949/呎
-(25年-08月)</t>
+(25年-08月-20日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -9479,7 +9479,7 @@
           <t>3 | 2133呎 (4+房)
 $15600万
 $73,136/呎
-(24年-12月)</t>
+(24年-12月-09日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -9502,7 +9502,7 @@
           <t>3 | 2133呎 (4+房)
 $15380万
 $72,105/呎
-(23年-05月)</t>
+(23年-05月-04日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -9548,7 +9548,7 @@
           <t>3 | 2133呎 (4+房)
 $14800万
 $69,386/呎
-(25年-06月)</t>
+(25年-06月-18日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -9732,7 +9732,7 @@
           <t>3 | 2065呎 (4+房)
 $12695万
 $61,477/呎
-(25年-04月)</t>
+(25年-04月-24日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -9740,7 +9740,7 @@
           <t>5 | 2029呎 (4+房)
 $12560万
 $61,902/呎
-(25年-10月)</t>
+(25年-10月-02日)</t>
         </is>
       </c>
     </row>
@@ -9866,7 +9866,7 @@
           <t>6 | 2927呎 (4+房)
 $37737万
 $128,927/呎
-(21年-04月)</t>
+(21年-04月-15日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -9882,7 +9882,7 @@
           <t>6 | 2112呎 (4+房)
 $18150万
 $85,938/呎
-(21年-08月)</t>
+(21年-08月-02日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -9890,7 +9890,7 @@
           <t>7 | 2256呎 (4+房)
 $20850万
 $92,420/呎
-(21年-08月)</t>
+(21年-08月-02日)</t>
         </is>
       </c>
     </row>
@@ -9905,7 +9905,7 @@
           <t>6 | 2112呎 (4+房)
 $19011万
 $90,014/呎
-(22年-06月)</t>
+(22年-06月-01日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -9913,7 +9913,7 @@
           <t>7 | 2256呎 (4+房)
 $20389万
 $90,376/呎
-(22年-06月)</t>
+(22年-06月-01日)</t>
         </is>
       </c>
     </row>
@@ -9951,7 +9951,7 @@
           <t>6 | 2112呎 (4+房)
 $17200万
 $81,439/呎
-(21年-11月)</t>
+(21年-11月-15日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -9959,7 +9959,7 @@
           <t>7 | 2256呎 (4+房)
 $19038万
 $84,388/呎
-(21年-08月)</t>
+(21年-08月-15日)</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
           <t>6 | 2112呎 (4+房)
 $16680万
 $78,977/呎
-(22年-01月)</t>
+(22年-01月-30日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -9982,7 +9982,7 @@
           <t>7 | 2256呎 (4+房)
 $18523万
 $82,107/呎
-(21年-10月)</t>
+(21年-10月-20日)</t>
         </is>
       </c>
     </row>
@@ -10005,7 +10005,7 @@
           <t>7 | 2256呎 (4+房)
 $18000万
 $79,787/呎
-(21年-10月)</t>
+(21年-10月-18日)</t>
         </is>
       </c>
     </row>
@@ -10020,7 +10020,7 @@
           <t>6 | 2112呎 (4+房)
 $15930万
 $75,426/呎
-(21年-10月)</t>
+(21年-10月-11日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -10028,7 +10028,7 @@
           <t>7 | 2256呎 (4+房)
 $17360万
 $76,950/呎
-(21年-10月)</t>
+(21年-10月-18日)</t>
         </is>
       </c>
     </row>
@@ -10043,7 +10043,7 @@
           <t>6 | 2112呎 (4+房)
 $15480万
 $73,295/呎
-(21年-09月)</t>
+(21年-09月-09日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -10051,7 +10051,7 @@
           <t>7 | 2256呎 (4+房)
 $16800万
 $74,468/呎
-(21年-04月)</t>
+(21年-04月-26日)</t>
         </is>
       </c>
     </row>
@@ -10066,7 +10066,7 @@
           <t>6 | 2112呎 (4+房)
 $14000万
 $66,288/呎
-(24年-05月)</t>
+(24年-05月-29日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -10097,7 +10097,7 @@
           <t>7 | 2256呎 (4+房)
 $16280万
 $72,163/呎
-(23年-04月)</t>
+(23年-04月-02日)</t>
         </is>
       </c>
     </row>
@@ -10112,7 +10112,7 @@
           <t>6 | 2112呎 (4+房)
 $14400万
 $68,182/呎
-(25年-09月)</t>
+(25年-09月-01日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -10120,7 +10120,7 @@
           <t>7 | 2256呎 (4+房)
 $15280万
 $67,730/呎
-(23年-03月)</t>
+(23年-03月-20日)</t>
         </is>
       </c>
     </row>
@@ -10135,7 +10135,7 @@
           <t>6 | 2112呎 (4+房)
 $13600万
 $64,394/呎
-(23年-12月)</t>
+(23年-12月-11日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -10181,7 +10181,7 @@
           <t>6 | 2112呎 (4+房)
 $13080万
 $61,932/呎
-(26年-07月)</t>
+(26年-07月-05日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -10189,7 +10189,7 @@
           <t>7 | 2256呎 (4+房)
 $14420万
 $63,918/呎
-(26年-07月)</t>
+(26年-07月-05日)</t>
         </is>
       </c>
     </row>
@@ -10227,7 +10227,7 @@
           <t>6 | 2112呎 (4+房)
 $11700万
 $55,398/呎
-(24年-07月)</t>
+(24年-07月-11日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -10235,7 +10235,7 @@
           <t>7 | 2256呎 (4+房)
 $13842万
 $61,357/呎
-(26年-01月)</t>
+(26年-01月-25日)</t>
         </is>
       </c>
     </row>
@@ -10250,7 +10250,7 @@
           <t>6 | 2112呎 (4+房)
 $11500万
 $54,451/呎
-(24年-06月)</t>
+(24年-06月-11日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -10296,7 +10296,7 @@
           <t>6 | 2032呎 (4+房)
 $12630万
 $62,156/呎
-(25年-03月)</t>
+(25年-03月-13日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -10304,7 +10304,7 @@
           <t>7 | 2176呎 (4+房)
 $15430万
 $70,910/呎
-(21年-10月)</t>
+(21年-10月-21日)</t>
         </is>
       </c>
     </row>
